--- a/cases/case_0001/Geometria.xlsx
+++ b/cases/case_0001/Geometria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\Proyectos python\StructureLab\cases\case_0001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDCF2A79-DF12-4214-BA60-334055A2CFD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD08EE7B-615A-4B10-BD44-B93C00E63F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{08B69389-F5AB-430C-A6FC-8A2E5D2BC54C}"/>
   </bookViews>
@@ -108,9 +108,6 @@
     <t>mm</t>
   </si>
   <si>
-    <t>CNT. 1 (12X25cm_FC21)</t>
-  </si>
-  <si>
     <t>CR21MPa</t>
   </si>
   <si>
@@ -129,9 +126,6 @@
     <t>628559b2-2b3c-4ecd-8436-24e0627c4f69</t>
   </si>
   <si>
-    <t>CNT. 1A (12X25cm_FC21)</t>
-  </si>
-  <si>
     <t>Red</t>
   </si>
   <si>
@@ -376,6 +370,12 @@
   </si>
   <si>
     <t>ACI 318-14</t>
+  </si>
+  <si>
+    <t>VCIM70X70FC24.5(SM)</t>
+  </si>
+  <si>
+    <t>VCIM50X50FC28</t>
   </si>
 </sst>
 </file>
@@ -854,7 +854,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -870,40 +870,40 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="D2" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="E2" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="F2" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="J2" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="K2" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="L2" s="8" t="s">
         <v>100</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -946,40 +946,40 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="G4" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="H4" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="K4" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="J4" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>112</v>
-      </c>
       <c r="L4" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1143,131 +1143,131 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>24</v>
-      </c>
       <c r="C4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4">
+        <v>700</v>
+      </c>
+      <c r="E4">
+        <v>700</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D4">
-        <v>150</v>
-      </c>
-      <c r="E4">
-        <v>250</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5" t="s">
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4" s="5" t="s">
+      <c r="S4" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5">
+        <v>500</v>
+      </c>
+      <c r="E5">
+        <v>500</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="S5" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5">
-        <v>250</v>
-      </c>
-      <c r="E5">
-        <v>120</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D6">
         <v>250</v>
@@ -1276,17 +1276,17 @@
         <v>250</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="J6">
         <v>1</v>
       </c>
@@ -1312,21 +1312,21 @@
         <v>1</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>350</v>
@@ -1335,57 +1335,57 @@
         <v>350</v>
       </c>
       <c r="F7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7" s="5" t="s">
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="S7" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8">
         <v>350</v>
@@ -1394,17 +1394,17 @@
         <v>350</v>
       </c>
       <c r="F8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="J8">
         <v>1</v>
       </c>
@@ -1430,21 +1430,21 @@
         <v>1</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9">
         <v>300</v>
@@ -1453,17 +1453,17 @@
         <v>300</v>
       </c>
       <c r="F9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="J9">
         <v>1</v>
       </c>
@@ -1489,21 +1489,21 @@
         <v>1</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10">
         <v>400</v>
@@ -1512,17 +1512,17 @@
         <v>350</v>
       </c>
       <c r="F10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="J10">
         <v>1</v>
       </c>
@@ -1548,21 +1548,21 @@
         <v>1</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="S10" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11">
         <v>400</v>
@@ -1571,17 +1571,17 @@
         <v>350</v>
       </c>
       <c r="F11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="J11">
         <v>1</v>
       </c>
@@ -1607,21 +1607,21 @@
         <v>1</v>
       </c>
       <c r="R11" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="S11" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12">
         <v>150</v>
@@ -1630,17 +1630,17 @@
         <v>150</v>
       </c>
       <c r="F12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="J12">
         <v>1</v>
       </c>
@@ -1666,21 +1666,21 @@
         <v>1</v>
       </c>
       <c r="R12" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S12" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13">
         <v>200</v>
@@ -1689,17 +1689,17 @@
         <v>200</v>
       </c>
       <c r="F13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="J13">
         <v>1</v>
       </c>
@@ -1725,21 +1725,21 @@
         <v>1</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>80</v>
@@ -1748,17 +1748,17 @@
         <v>50</v>
       </c>
       <c r="F14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="J14">
         <v>0.01</v>
       </c>
@@ -1784,21 +1784,21 @@
         <v>1</v>
       </c>
       <c r="R14" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="S14" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15">
         <v>250</v>
@@ -1807,17 +1807,17 @@
         <v>350</v>
       </c>
       <c r="F15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="J15">
         <v>1</v>
       </c>
@@ -1843,21 +1843,21 @@
         <v>1</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16">
         <v>400</v>
@@ -1866,17 +1866,17 @@
         <v>400</v>
       </c>
       <c r="F16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="J16">
         <v>1</v>
       </c>
@@ -1902,21 +1902,21 @@
         <v>1</v>
       </c>
       <c r="R16" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17">
         <v>250</v>
@@ -1925,16 +1925,16 @@
         <v>200</v>
       </c>
       <c r="F17" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J17">
         <v>0.01</v>
@@ -1961,21 +1961,21 @@
         <v>1</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18">
         <v>350</v>
@@ -1984,16 +1984,16 @@
         <v>250</v>
       </c>
       <c r="F18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="H18">
         <v>1</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J18">
         <v>0.01</v>
@@ -2020,21 +2020,21 @@
         <v>1</v>
       </c>
       <c r="R18" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="S18" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19">
         <v>250</v>
@@ -2043,16 +2043,16 @@
         <v>120</v>
       </c>
       <c r="F19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="H19">
         <v>1</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J19">
         <v>0.01</v>
@@ -2079,21 +2079,21 @@
         <v>1</v>
       </c>
       <c r="R19" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="S19" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D20">
         <v>250</v>
@@ -2102,16 +2102,16 @@
         <v>250</v>
       </c>
       <c r="F20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="H20">
         <v>1</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J20">
         <v>0.01</v>
@@ -2138,21 +2138,21 @@
         <v>1</v>
       </c>
       <c r="R20" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S20" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21">
         <v>350</v>
@@ -2161,16 +2161,16 @@
         <v>350</v>
       </c>
       <c r="F21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="H21">
         <v>1</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2197,21 +2197,21 @@
         <v>1</v>
       </c>
       <c r="R21" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="S21" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D22">
         <v>350</v>
@@ -2220,16 +2220,16 @@
         <v>350</v>
       </c>
       <c r="F22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="H22">
         <v>1</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2256,21 +2256,21 @@
         <v>1</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23">
         <v>350</v>
@@ -2279,16 +2279,16 @@
         <v>300</v>
       </c>
       <c r="F23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="H23">
         <v>1</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2315,21 +2315,21 @@
         <v>1</v>
       </c>
       <c r="R23" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="S23" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24">
         <v>350</v>
@@ -2338,16 +2338,16 @@
         <v>450</v>
       </c>
       <c r="F24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="H24">
         <v>1</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -2374,21 +2374,21 @@
         <v>1</v>
       </c>
       <c r="R24" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S24" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D25">
         <v>350</v>
@@ -2397,16 +2397,16 @@
         <v>400</v>
       </c>
       <c r="F25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="H25">
         <v>1</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -2433,21 +2433,21 @@
         <v>1</v>
       </c>
       <c r="R25" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S25" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D26">
         <v>350</v>
@@ -2456,16 +2456,16 @@
         <v>400</v>
       </c>
       <c r="F26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -2492,21 +2492,21 @@
         <v>1</v>
       </c>
       <c r="R26" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="S26" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D27">
         <v>300</v>
@@ -2515,16 +2515,16 @@
         <v>300</v>
       </c>
       <c r="F27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="H27">
         <v>1</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -2551,21 +2551,21 @@
         <v>1</v>
       </c>
       <c r="R27" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="S27" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D28">
         <v>110</v>
@@ -2574,17 +2574,17 @@
         <v>80</v>
       </c>
       <c r="F28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H28">
-        <v>1</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="J28">
         <v>1</v>
       </c>
@@ -2610,21 +2610,21 @@
         <v>1</v>
       </c>
       <c r="R28" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D29">
         <v>180</v>
@@ -2633,17 +2633,17 @@
         <v>80</v>
       </c>
       <c r="F29" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G29" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H29">
-        <v>1</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="J29">
         <v>1</v>
       </c>
@@ -2669,10 +2669,10 @@
         <v>1</v>
       </c>
       <c r="R29" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="S29" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
